--- a/data/trending_integrated_20260921_12.xlsx
+++ b/data/trending_integrated_20260921_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G2" t="n">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203172135535</v>
+        <v>203385346535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10810</v>
+        <v>10790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.84%</t>
+          <t>'+19.62%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
         <v>208</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>213937263600</v>
+        <v>217091579420</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5840</v>
+        <v>5850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.55%</t>
+          <t>'+7.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>143</v>
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>58962165890</v>
+        <v>59173285180</v>
       </c>
       <c r="P4" t="n">
         <v>13140</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31550</v>
+        <v>31800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.41%</t>
+          <t>'+7.25%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.48</v>
       </c>
       <c r="E5" t="n">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F5" t="n">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G5" t="n">
-        <v>1540</v>
+        <v>1630</v>
       </c>
       <c r="H5" t="n">
         <v>16.67</v>
@@ -886,7 +886,7 @@
         <v>17.15</v>
       </c>
       <c r="O5" t="n">
-        <v>25413173625</v>
+        <v>25847805050</v>
       </c>
       <c r="P5" t="n">
         <v>69200</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207500</v>
+        <v>208000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.81%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H6" t="n">
         <v>75.44</v>
@@ -969,7 +969,7 @@
         <v>199800</v>
       </c>
       <c r="L6" t="n">
-        <v>207500</v>
+        <v>208000</v>
       </c>
       <c r="M6" t="n">
         <v>199600</v>
@@ -978,7 +978,7 @@
         <v>75.53</v>
       </c>
       <c r="O6" t="n">
-        <v>526937998800</v>
+        <v>543587978550</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11080</v>
+        <v>273000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.32%</t>
+          <t>'+4.60%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>500</v>
       </c>
       <c r="G7" t="n">
-        <v>207</v>
+        <v>2671</v>
       </c>
       <c r="H7" t="n">
-        <v>18.29</v>
+        <v>46.46</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10520</v>
+        <v>261000</v>
       </c>
       <c r="K7" t="n">
-        <v>10780</v>
+        <v>264000</v>
       </c>
       <c r="L7" t="n">
-        <v>12190</v>
+        <v>273500</v>
       </c>
       <c r="M7" t="n">
-        <v>10590</v>
+        <v>263500</v>
       </c>
       <c r="N7" t="n">
-        <v>18.13</v>
+        <v>46.48</v>
       </c>
       <c r="O7" t="n">
-        <v>168865612600</v>
+        <v>3342505046500</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1760</v>
+        <v>81100</v>
       </c>
       <c r="R7" t="n">
-        <v>-6000</v>
+        <v>3622000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>391000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등 및 나스닥 선물 상승에 따른 재진입 언급. 20% 상승 기대와 더불어, 단기 고점 및 하락 가능성도 함께 제시.</t>
+          <t>배당락일 이전 매수세 유입 기대감 및 3분기 실적 발표 예정, 자사주 소각 및 배당 관련 긍정적 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '나스닥', '추격']</t>
+          <t>['배당금', '실적 발표', '자사주 소각']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>272750</v>
+        <v>10990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.50%</t>
+          <t>'+4.47%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>497</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>2682</v>
+        <v>221</v>
       </c>
       <c r="H8" t="n">
-        <v>46.46</v>
+        <v>18.29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>261000</v>
+        <v>10520</v>
       </c>
       <c r="K8" t="n">
-        <v>264000</v>
+        <v>10780</v>
       </c>
       <c r="L8" t="n">
-        <v>273000</v>
+        <v>12190</v>
       </c>
       <c r="M8" t="n">
-        <v>263500</v>
+        <v>10590</v>
       </c>
       <c r="N8" t="n">
-        <v>46.48</v>
+        <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>3189758272500</v>
+        <v>171144628360</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>81100</v>
+        <v>1760</v>
       </c>
       <c r="R8" t="n">
-        <v>3622000</v>
+        <v>-6000</v>
       </c>
       <c r="S8" t="n">
-        <v>391000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>신한증권 시스템 오류 발생 속, 27만원 목표주가 및 3분기 실적 발표, 자사주 소각/배당 관련 언급. 10월 이후 상승 전망.</t>
+          <t>미국 증시 광통신주 급등 및 선물 지수 상승에 따른 긍정적 재진입 신호 감지. 단기 고점 및 하락 가능성에 대한 주의 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성전자', '신한증권', '실적']</t>
+          <t>['광통신주', '재진입', '고점']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1871000</v>
+        <v>1875000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.97%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>478</v>
       </c>
       <c r="G9" t="n">
-        <v>2333</v>
+        <v>2289</v>
       </c>
       <c r="H9" t="n">
         <v>50.23</v>
@@ -1254,7 +1254,7 @@
         <v>50.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2627627749500</v>
+        <v>2712597015000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 선물 시장 상승 및 반도체 수출 호조 기대감. 신한증권 시스템 오류로 거래 차질 발생, 193만 돌파 시 추가 상승 전망.</t>
+          <t>미국 증시 엔비디아 등 반도체 관련주 급등에 따른 상승 기대감 형성. 신한증권 시스템 접속 오류로 인한 거래 불편 호소.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체', '신한증권']</t>
+          <t>['반도체 수출', '상승 기대감', '시스템 오류']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26750</v>
+        <v>26700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.19%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H10" t="n">
         <v>2.11</v>
@@ -1346,7 +1346,7 @@
         <v>2.41</v>
       </c>
       <c r="O10" t="n">
-        <v>106152942200</v>
+        <v>107725554600</v>
       </c>
       <c r="P10" t="n">
         <v>59600</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13790</v>
+        <v>13810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.58%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
@@ -1438,7 +1438,7 @@
         <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>60688048845</v>
+        <v>61265054340</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4145</v>
+        <v>4135</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.78%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.22</v>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="H12" t="n">
         <v>0.33</v>
@@ -1530,7 +1530,7 @@
         <v>0.55</v>
       </c>
       <c r="O12" t="n">
-        <v>27380558881</v>
+        <v>27540381609</v>
       </c>
       <c r="P12" t="n">
         <v>6480</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78500</v>
+        <v>78300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.88%</t>
+          <t>'-2.12%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G13" t="n">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="H13" t="n">
         <v>10.58</v>
@@ -1622,7 +1622,7 @@
         <v>10.68</v>
       </c>
       <c r="O13" t="n">
-        <v>90521060450</v>
+        <v>91415947050</v>
       </c>
       <c r="P13" t="n">
         <v>184000</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18540</v>
+        <v>18460</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>63050485620</v>
+        <v>63818882765</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17710</v>
+        <v>17640</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-3.71%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G15" t="n">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="H15" t="n">
         <v>7.9</v>
@@ -1806,7 +1806,7 @@
         <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>182353774615</v>
+        <v>184374234480</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 급등에 따른 영향 및 기관 매수세 확인. 연말, 내년 초까지 상승 전망과 함께 조정 시 매수 기회 제시.</t>
+          <t>미국 광통신 AI주 및 관련 종목 급등에 따른 긍정적 영향 기대. 연말, 내년 초까지의 상승 전망과 조정 시 매수 기회 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대한광통신', 'AI', '기관']</t>
+          <t>['광통신 AI주', '수출 기록', '조정 매수']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30025</v>
+        <v>30050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.53%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.48</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G16" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H16" t="n">
         <v>11.92</v>
@@ -1898,7 +1898,7 @@
         <v>11.44</v>
       </c>
       <c r="O16" t="n">
-        <v>67941435800</v>
+        <v>69006740200</v>
       </c>
       <c r="P16" t="n">
         <v>75900</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>311000</v>
+        <v>310500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-5.05%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>74462274000</v>
+        <v>75474516500</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27650</v>
+        <v>27550</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-26.07%</t>
+          <t>'-26.34%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="F18" t="n">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G18" t="n">
-        <v>1225</v>
+        <v>1246</v>
       </c>
       <c r="H18" t="n">
         <v>7.09</v>
@@ -2082,7 +2082,7 @@
         <v>7.08</v>
       </c>
       <c r="O18" t="n">
-        <v>85804928950</v>
+        <v>88464884975</v>
       </c>
       <c r="P18" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_12.xlsx
+++ b/data/trending_integrated_20260921_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203385346535</v>
+        <v>203478771535</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미국 타임지 선정 '세계 최고 헬스테크 기업' 선정 소식에 따른 급등. 2주간의 급락 이후 상승 전환하며 전고점 돌파 기대감 형성.</t>
+          <t>미국 시사주간지 타임 선정 '세계 최고 헬스테크 기업' 선정으로 인한 주가 급등. 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스카이랩스', '헬스테크', '타임지']</t>
+          <t>['스카이랩스', '헬스테크', '선정']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10790</v>
+        <v>10900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.62%</t>
+          <t>'+20.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>217091579420</v>
+        <v>220839371260</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5850</v>
+        <v>20600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+7.73%</t>
+          <t>'+11.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.31</v>
+        <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19</v>
+        <v>1.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,91 +779,91 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5430</v>
+        <v>18470</v>
       </c>
       <c r="K4" t="n">
-        <v>5710</v>
+        <v>18640</v>
       </c>
       <c r="L4" t="n">
-        <v>6280</v>
+        <v>21600</v>
       </c>
       <c r="M4" t="n">
-        <v>5600</v>
+        <v>18590</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>59173285180</v>
+        <v>74403414695</v>
       </c>
       <c r="P4" t="n">
-        <v>13140</v>
+        <v>21600</v>
       </c>
       <c r="Q4" t="n">
-        <v>3725</v>
+        <v>9900</v>
       </c>
       <c r="R4" t="n">
-        <v>-344000</v>
+        <v>53000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
+          <t>인제니아테라퓨틱스 주가 상승 기대감 및 ADC 관련 확장 언급. 삼중항체 개발 관련 긍정적 뉴스 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비트코인', '공매도', '신한투자증권']</t>
+          <t>['인제니아테라퓨틱스', 'ADC', '삼중항체']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31800</v>
+        <v>5870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.25%</t>
+          <t>'+8.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.48</v>
+        <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>380</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>1630</v>
+        <v>145</v>
       </c>
       <c r="H5" t="n">
-        <v>16.67</v>
+        <v>0.19</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29650</v>
+        <v>5430</v>
       </c>
       <c r="K5" t="n">
-        <v>30400</v>
+        <v>5710</v>
       </c>
       <c r="L5" t="n">
-        <v>33400</v>
+        <v>6280</v>
       </c>
       <c r="M5" t="n">
-        <v>29400</v>
+        <v>5600</v>
       </c>
       <c r="N5" t="n">
-        <v>17.15</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>25847805050</v>
+        <v>59305488820</v>
       </c>
       <c r="P5" t="n">
-        <v>69200</v>
+        <v>13140</v>
       </c>
       <c r="Q5" t="n">
-        <v>24150</v>
+        <v>3725</v>
       </c>
       <c r="R5" t="n">
-        <v>-148000</v>
+        <v>-344000</v>
       </c>
       <c r="S5" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
+          <t>비트코인 가격 상승 반전에 따라 우리기술투자 주가 급등. 신한투자증권 공매도 의혹 제기 및 민원 제기 움직임. 7천 원 목표가 제시하며 비트코인 흐름에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['FDA', '신약 승인', '리보세라닙']</t>
+          <t>['비트코인', '공매도', '신한투자증권']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,91 +919,91 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>208000</v>
+        <v>31600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+6.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.09</v>
+        <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>62</v>
+        <v>387</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="G6" t="n">
-        <v>308</v>
+        <v>1673</v>
       </c>
       <c r="H6" t="n">
-        <v>75.44</v>
+        <v>16.67</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>196100</v>
+        <v>29650</v>
       </c>
       <c r="K6" t="n">
-        <v>199800</v>
+        <v>30400</v>
       </c>
       <c r="L6" t="n">
-        <v>208000</v>
+        <v>33400</v>
       </c>
       <c r="M6" t="n">
-        <v>199600</v>
+        <v>29400</v>
       </c>
       <c r="N6" t="n">
-        <v>75.53</v>
+        <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>543587978550</v>
+        <v>26205362900</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>64700</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>504000</v>
+        <v>-148000</v>
       </c>
       <c r="S6" t="n">
-        <v>-25000</v>
+        <v>-7000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
+          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '자사주', '외인']</t>
+          <t>['FDA', '신약 승인', '리보세라닙']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>273000</v>
+        <v>208000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.60%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>500</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>2671</v>
+        <v>315</v>
       </c>
       <c r="H7" t="n">
-        <v>46.46</v>
+        <v>75.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>261000</v>
+        <v>196100</v>
       </c>
       <c r="K7" t="n">
-        <v>264000</v>
+        <v>199800</v>
       </c>
       <c r="L7" t="n">
-        <v>273500</v>
+        <v>208000</v>
       </c>
       <c r="M7" t="n">
-        <v>263500</v>
+        <v>199600</v>
       </c>
       <c r="N7" t="n">
-        <v>46.48</v>
+        <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3342505046500</v>
+        <v>550989545800</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>81100</v>
+        <v>64700</v>
       </c>
       <c r="R7" t="n">
-        <v>3622000</v>
+        <v>504000</v>
       </c>
       <c r="S7" t="n">
-        <v>391000</v>
+        <v>-25000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>배당락일 이전 매수세 유입 기대감 및 3분기 실적 발표 예정, 자사주 소각 및 배당 관련 긍정적 전망. 신한증권 시스템 오류에 대한 불만 제기.</t>
+          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당금', '실적 발표', '자사주 소각']</t>
+          <t>['배당', '자사주', '외인']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10990</v>
+        <v>11150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.47%</t>
+          <t>'+5.99%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="H8" t="n">
         <v>18.29</v>
@@ -1162,7 +1162,7 @@
         <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>171144628360</v>
+        <v>173041986740</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 증시 광통신주 급등 및 선물 지수 상승에 따른 긍정적 재진입 신호 감지. 단기 고점 및 하락 가능성에 대한 주의 언급.</t>
+          <t>미국 광통신주 급등에 따른 국내 광전자 주가 상승 기대감. 그러나 단기 급락 가능성도 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신주', '재진입', '고점']</t>
+          <t>['광통신주', '추세', '급등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1875000</v>
+        <v>274000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.97%</t>
+          <t>'+4.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E9" t="n">
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="G9" t="n">
-        <v>2289</v>
+        <v>2745</v>
       </c>
       <c r="H9" t="n">
-        <v>50.23</v>
+        <v>46.46</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1857000</v>
+        <v>261000</v>
       </c>
       <c r="K9" t="n">
-        <v>1872000</v>
+        <v>264000</v>
       </c>
       <c r="L9" t="n">
-        <v>1888000</v>
+        <v>274000</v>
       </c>
       <c r="M9" t="n">
-        <v>1847000</v>
+        <v>263500</v>
       </c>
       <c r="N9" t="n">
-        <v>50.1</v>
+        <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>2712597015000</v>
+        <v>3452200669250</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>333000</v>
+        <v>81100</v>
       </c>
       <c r="R9" t="n">
-        <v>-64000</v>
+        <v>3622000</v>
       </c>
       <c r="S9" t="n">
-        <v>91000</v>
+        <v>391000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 엔비디아 등 반도체 관련주 급등에 따른 상승 기대감 형성. 신한증권 시스템 접속 오류로 인한 거래 불편 호소.</t>
+          <t>삼성전자 3분기 잠정 실적 발표 및 4분기 자사주 소각/배당 관련 기대감. 일부 증권사 목표가 하향 조정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['반도체 수출', '상승 기대감', '시스템 오류']</t>
+          <t>['삼성전자', '배당금', '실적']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,99 +1292,99 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26700</v>
+        <v>1878000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3</v>
+        <v>0.13</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>482</v>
       </c>
       <c r="G10" t="n">
-        <v>133</v>
+        <v>2248</v>
       </c>
       <c r="H10" t="n">
-        <v>2.11</v>
+        <v>50.23</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26800</v>
+        <v>1857000</v>
       </c>
       <c r="K10" t="n">
-        <v>27400</v>
+        <v>1872000</v>
       </c>
       <c r="L10" t="n">
-        <v>27750</v>
+        <v>1888000</v>
       </c>
       <c r="M10" t="n">
-        <v>25650</v>
+        <v>1847000</v>
       </c>
       <c r="N10" t="n">
-        <v>2.41</v>
+        <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>107725554600</v>
+        <v>2796447366500</v>
       </c>
       <c r="P10" t="n">
-        <v>59600</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1030</v>
+        <v>333000</v>
       </c>
       <c r="R10" t="n">
-        <v>-234000</v>
+        <v>-64000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>91000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>미국 증시 엔비디아 등 반도체 관련주 급등에 따른 SK하이닉스 주가 상승 기대감. 신한증권 앱 오류로 인한 불편.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['SK하이닉스', '반도체', '상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13810</v>
+        <v>13720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'-1.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
@@ -1438,7 +1438,7 @@
         <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>61265054340</v>
+        <v>61747499450</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4135</v>
+        <v>26500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.22</v>
+        <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>249</v>
+        <v>134</v>
       </c>
       <c r="H12" t="n">
-        <v>0.33</v>
+        <v>2.11</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4220</v>
+        <v>26800</v>
       </c>
       <c r="K12" t="n">
-        <v>4220</v>
+        <v>27400</v>
       </c>
       <c r="L12" t="n">
-        <v>4415</v>
+        <v>27750</v>
       </c>
       <c r="M12" t="n">
-        <v>4105</v>
+        <v>25650</v>
       </c>
       <c r="N12" t="n">
-        <v>0.55</v>
+        <v>2.41</v>
       </c>
       <c r="O12" t="n">
-        <v>27540381609</v>
+        <v>109205991400</v>
       </c>
       <c r="P12" t="n">
-        <v>6480</v>
+        <v>59600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1738</v>
+        <v>1030</v>
       </c>
       <c r="R12" t="n">
-        <v>208000</v>
+        <v>-234000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['미버스', '거래량', '재료소멸']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,99 +1568,99 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78300</v>
+        <v>4125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.12%</t>
+          <t>'-2.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="E13" t="n">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>677</v>
+        <v>261</v>
       </c>
       <c r="H13" t="n">
-        <v>10.58</v>
+        <v>0.33</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>80000</v>
+        <v>4220</v>
       </c>
       <c r="K13" t="n">
-        <v>82900</v>
+        <v>4220</v>
       </c>
       <c r="L13" t="n">
-        <v>83000</v>
+        <v>4415</v>
       </c>
       <c r="M13" t="n">
-        <v>75300</v>
+        <v>4105</v>
       </c>
       <c r="N13" t="n">
-        <v>10.68</v>
+        <v>0.55</v>
       </c>
       <c r="O13" t="n">
-        <v>91415947050</v>
+        <v>27725953804</v>
       </c>
       <c r="P13" t="n">
-        <v>184000</v>
+        <v>6480</v>
       </c>
       <c r="Q13" t="n">
-        <v>44750</v>
+        <v>1738</v>
       </c>
       <c r="R13" t="n">
-        <v>-499000</v>
+        <v>208000</v>
       </c>
       <c r="S13" t="n">
-        <v>-56000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유럽 K-방산 드론 시장 진출 관련 뉴스 언급. 공매도 금지 및 10만원대 상승 기대와 함께, 8만원 돌파 시 추가 상승 가능성 제시.</t>
+          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['한화시스템', '방산', '드론']</t>
+          <t>['미버스', '거래량', '재료소멸']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18460</v>
+        <v>18480</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.27%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
         <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="H14" t="n">
         <v>10.74</v>
@@ -1714,7 +1714,7 @@
         <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>63818882765</v>
+        <v>64702242450</v>
       </c>
       <c r="P14" t="n">
         <v>40350</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대우건설, 공매도 장부 조작 의혹 및 대차해지 운동 동참 호소. 주가 하락 추세 및 기관 매매 관련 논의.</t>
+          <t>공매도 세력에 대한 비판과 대차해지 운동 촉구. 주가 상승에 대한 기대감 있으나, 근거는 부족.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1759,83 +1759,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17640</v>
+        <v>78100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.71%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.29</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>881</v>
+        <v>684</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>10.58</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18320</v>
+        <v>80000</v>
       </c>
       <c r="K15" t="n">
-        <v>18450</v>
+        <v>82900</v>
       </c>
       <c r="L15" t="n">
-        <v>18590</v>
+        <v>83000</v>
       </c>
       <c r="M15" t="n">
-        <v>17590</v>
+        <v>75300</v>
       </c>
       <c r="N15" t="n">
-        <v>4.61</v>
+        <v>10.68</v>
       </c>
       <c r="O15" t="n">
-        <v>184374234480</v>
+        <v>92393058900</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>184000</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>44750</v>
       </c>
       <c r="R15" t="n">
-        <v>-1480000</v>
+        <v>-499000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-56000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 AI주 및 관련 종목 급등에 따른 긍정적 영향 기대. 연말, 내년 초까지의 상승 전망과 조정 시 매수 기회 언급.</t>
+          <t>유럽 K-방산 드론 시장 진출 관련 뉴스 언급. 공매도 금지 및 10만원대 상승 기대와 함께, 8만원 돌파 시 추가 상승 가능성 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신 AI주', '수출 기록', '조정 매수']</t>
+          <t>['한화시스템', '방산', '드론']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30050</v>
+        <v>17650</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-3.66%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.48</v>
+        <v>3.29</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
-        <v>136</v>
+        <v>898</v>
       </c>
       <c r="H16" t="n">
-        <v>11.92</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>31450</v>
+        <v>18320</v>
       </c>
       <c r="K16" t="n">
+        <v>18450</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18590</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17590</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="O16" t="n">
+        <v>186918834590</v>
+      </c>
+      <c r="P16" t="n">
         <v>31500</v>
       </c>
-      <c r="L16" t="n">
-        <v>31550</v>
-      </c>
-      <c r="M16" t="n">
-        <v>29950</v>
-      </c>
-      <c r="N16" t="n">
-        <v>11.44</v>
-      </c>
-      <c r="O16" t="n">
-        <v>69006740200</v>
-      </c>
-      <c r="P16" t="n">
-        <v>75900</v>
-      </c>
       <c r="Q16" t="n">
-        <v>15000</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-420000</v>
+        <v>-1480000</v>
       </c>
       <c r="S16" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한전선, 금일 하락세 속 반도체 소부장 순환매 관련 언급. 장기 이평선 저항 및 매물대 관련 논의.</t>
+          <t>미국 광통신주 급등에 따른 대한광통신 주가 상승 기대감. 연말/내년 초까지 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['하락', '순환매', '매물대']</t>
+          <t>['대한광통신', '광통신주', '전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>310500</v>
+        <v>30000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.05%</t>
+          <t>'-4.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.66</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="H17" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>327000</v>
+        <v>31450</v>
       </c>
       <c r="K17" t="n">
-        <v>324000</v>
+        <v>31500</v>
       </c>
       <c r="L17" t="n">
-        <v>340500</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>308500</v>
+        <v>29950</v>
       </c>
       <c r="N17" t="n">
-        <v>1.96</v>
+        <v>11.44</v>
       </c>
       <c r="O17" t="n">
-        <v>75474516500</v>
+        <v>71768482750</v>
       </c>
       <c r="P17" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>-52000</v>
+        <v>-420000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 외인 매수세 유입.</t>
+          <t>대한전선 주가 하락에 대한 실망감 표현. 추석 연휴 전 추가 하락 예측.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신고가', '외국인', '고평가']</t>
+          <t>['대한전선', '하락', '추세']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,86 +2028,86 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>오름테라퓨틱</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27550</v>
+        <v>311000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-26.34%</t>
+          <t>'-4.89%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>1.66</v>
       </c>
       <c r="E18" t="n">
-        <v>677</v>
+        <v>108</v>
       </c>
       <c r="F18" t="n">
-        <v>351</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>1246</v>
+        <v>221</v>
       </c>
       <c r="H18" t="n">
-        <v>7.09</v>
+        <v>3.62</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>37400</v>
+        <v>327000</v>
       </c>
       <c r="K18" t="n">
-        <v>26450</v>
+        <v>324000</v>
       </c>
       <c r="L18" t="n">
-        <v>29050</v>
+        <v>340500</v>
       </c>
       <c r="M18" t="n">
-        <v>26200</v>
+        <v>308500</v>
       </c>
       <c r="N18" t="n">
-        <v>7.08</v>
+        <v>1.96</v>
       </c>
       <c r="O18" t="n">
-        <v>88464884975</v>
+        <v>76816086000</v>
       </c>
       <c r="P18" t="n">
-        <v>146600</v>
+        <v>635000</v>
       </c>
       <c r="Q18" t="n">
-        <v>26200</v>
+        <v>52600</v>
       </c>
       <c r="R18" t="n">
-        <v>163000</v>
+        <v>-52000</v>
       </c>
       <c r="S18" t="n">
-        <v>30000</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['임상', '하한가', '바이오']</t>
+          <t>['신고가', '외국인', '고평가']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2119,6 +2119,98 @@
         </is>
       </c>
       <c r="Z18" t="inlineStr">
+        <is>
+          <t>000500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>27950</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-25.27%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" t="n">
+        <v>690</v>
+      </c>
+      <c r="F19" t="n">
+        <v>354</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1253</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>37400</v>
+      </c>
+      <c r="K19" t="n">
+        <v>26450</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29050</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26200</v>
+      </c>
+      <c r="N19" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O19" t="n">
+        <v>89881053750</v>
+      </c>
+      <c r="P19" t="n">
+        <v>146600</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>26200</v>
+      </c>
+      <c r="R19" t="n">
+        <v>163000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>임상 진행 관련 불확실성 및 연속 하한가 발생. 투자자들의 신중한 접근 요구.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['임상', '하한가', '바이오']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>475830</t>
         </is>

--- a/data/trending_integrated_20260921_12.xlsx
+++ b/data/trending_integrated_20260921_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203478771535</v>
+        <v>203601158285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10900</v>
+        <v>10780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.84%</t>
+          <t>'+19.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>220839371260</v>
+        <v>223072164600</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20600</v>
+        <v>20550</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.53%</t>
+          <t>'+11.26%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>74403414695</v>
+        <v>75487475370</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스 주가 상승 기대감 및 ADC 관련 확장 언급. 삼중항체 개발 관련 긍정적 뉴스 기대.</t>
+          <t>신규형냐들의 진입 및 21000원 안착 기대, 키트루다 능가 삼중항체 기술 개발.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인제니아테라퓨틱스', 'ADC', '삼중항체']</t>
+          <t>['인제니아테라퓨틱스', '삼중항체', '신규진입']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5870</v>
+        <v>5860</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+8.10%</t>
+          <t>'+7.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H5" t="n">
         <v>0.19</v>
@@ -886,7 +886,7 @@
         <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>59305488820</v>
+        <v>59520532470</v>
       </c>
       <c r="P5" t="n">
         <v>13140</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.58%</t>
+          <t>'+7.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="F6" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G6" t="n">
-        <v>1673</v>
+        <v>1716</v>
       </c>
       <c r="H6" t="n">
         <v>16.67</v>
@@ -978,7 +978,7 @@
         <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>26205362900</v>
+        <v>26456547350</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -1038,13 +1038,13 @@
         <v>-0.09</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H7" t="n">
         <v>75.44</v>
@@ -1070,7 +1070,7 @@
         <v>75.53</v>
       </c>
       <c r="O7" t="n">
-        <v>550989545800</v>
+        <v>558186172550</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11150</v>
+        <v>11110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.99%</t>
+          <t>'+5.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="H8" t="n">
         <v>18.29</v>
@@ -1162,7 +1162,7 @@
         <v>18.13</v>
       </c>
       <c r="O8" t="n">
-        <v>173041986740</v>
+        <v>173832762205</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 국내 광전자 주가 상승 기대감. 그러나 단기 급락 가능성도 언급.</t>
+          <t>미국 시장 광통신주 급등에 따른 재진입 및 20% 상승 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신주', '추세', '급등']</t>
+          <t>['광통신주', '재진입', '폭등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>274000</v>
+        <v>273500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.98%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G9" t="n">
-        <v>2745</v>
+        <v>2840</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3452200669250</v>
+        <v>3588253415250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자 3분기 잠정 실적 발표 및 4분기 자사주 소각/배당 관련 기대감. 일부 증권사 목표가 하향 조정.</t>
+          <t>추석 전 30만원 돌파 기대 및 3분기 실적 발표 및 배당금 지급 예정.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['삼성전자', '배당금', '실적']</t>
+          <t>['삼성전자', '배당금', '실적발표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1878000</v>
+        <v>1873000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+0.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>2248</v>
+        <v>2276</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2796447366500</v>
+        <v>2859853846000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 엔비디아 등 반도체 관련주 급등에 따른 SK하이닉스 주가 상승 기대감. 신한증권 앱 오류로 인한 불편.</t>
+          <t>미국 반도체주 급등에 따른 SK하이닉스 20만원 돌파 및 상승세 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체', '상승']</t>
+          <t>['SK하이닉스', '반도체', '상승세']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13720</v>
+        <v>13690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.08%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
@@ -1438,7 +1438,7 @@
         <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>61747499450</v>
+        <v>62345385720</v>
       </c>
       <c r="P11" t="n">
         <v>30200</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26500</v>
+        <v>26450</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H12" t="n">
         <v>2.11</v>
@@ -1530,7 +1530,7 @@
         <v>2.41</v>
       </c>
       <c r="O12" t="n">
-        <v>109205991400</v>
+        <v>110469973225</v>
       </c>
       <c r="P12" t="n">
         <v>59600</v>
@@ -1575,123 +1575,123 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4125</v>
+        <v>18470</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.25%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.22</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
+        <v>336</v>
       </c>
       <c r="H13" t="n">
-        <v>0.33</v>
+        <v>10.74</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4220</v>
+        <v>18910</v>
       </c>
       <c r="K13" t="n">
-        <v>4220</v>
+        <v>19050</v>
       </c>
       <c r="L13" t="n">
-        <v>4415</v>
+        <v>19050</v>
       </c>
       <c r="M13" t="n">
-        <v>4105</v>
+        <v>18090</v>
       </c>
       <c r="N13" t="n">
-        <v>0.55</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>27725953804</v>
+        <v>65419531020</v>
       </c>
       <c r="P13" t="n">
-        <v>6480</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>1738</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>208000</v>
+        <v>-673000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-88000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
+          <t>공매도 장부 조작 의혹 제기 및 대차해지 운동 동참 요구.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['미버스', '거래량', '재료소멸']</t>
+          <t>['대우건설', '공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18480</v>
+        <v>78100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.27%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>322</v>
+        <v>691</v>
       </c>
       <c r="H14" t="n">
-        <v>10.74</v>
+        <v>10.58</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18910</v>
+        <v>80000</v>
       </c>
       <c r="K14" t="n">
-        <v>19050</v>
+        <v>82900</v>
       </c>
       <c r="L14" t="n">
-        <v>19050</v>
+        <v>83000</v>
       </c>
       <c r="M14" t="n">
-        <v>18090</v>
+        <v>75300</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="O14" t="n">
-        <v>64702242450</v>
+        <v>93833864900</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>184000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>44750</v>
       </c>
       <c r="R14" t="n">
-        <v>-673000</v>
+        <v>-499000</v>
       </c>
       <c r="S14" t="n">
-        <v>-88000</v>
+        <v>-56000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 비판과 대차해지 운동 촉구. 주가 상승에 대한 기대감 있으나, 근거는 부족.</t>
+          <t>K-방산 시장 성장 및 한화시스템의 유럽 드론 시장 진출 기대, 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '추세']</t>
+          <t>['한화시스템', 'K-방산', '드론']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,99 +1752,99 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>272210</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78100</v>
+        <v>4115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.1</v>
+        <v>-0.22</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>684</v>
+        <v>275</v>
       </c>
       <c r="H15" t="n">
-        <v>10.58</v>
+        <v>0.33</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>80000</v>
+        <v>4220</v>
       </c>
       <c r="K15" t="n">
-        <v>82900</v>
+        <v>4220</v>
       </c>
       <c r="L15" t="n">
-        <v>83000</v>
+        <v>4415</v>
       </c>
       <c r="M15" t="n">
-        <v>75300</v>
+        <v>4105</v>
       </c>
       <c r="N15" t="n">
-        <v>10.68</v>
+        <v>0.55</v>
       </c>
       <c r="O15" t="n">
-        <v>92393058900</v>
+        <v>27983982834</v>
       </c>
       <c r="P15" t="n">
-        <v>184000</v>
+        <v>6480</v>
       </c>
       <c r="Q15" t="n">
-        <v>44750</v>
+        <v>1738</v>
       </c>
       <c r="R15" t="n">
-        <v>-499000</v>
+        <v>208000</v>
       </c>
       <c r="S15" t="n">
-        <v>-56000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유럽 K-방산 드론 시장 진출 관련 뉴스 언급. 공매도 금지 및 10만원대 상승 기대와 함께, 8만원 돌파 시 추가 상승 가능성 제시.</t>
+          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['한화시스템', '방산', '드론']</t>
+          <t>['미버스', '거래량', '재료소멸']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>272210</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17650</v>
+        <v>17630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.66%</t>
+          <t>'-3.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>197</v>
       </c>
       <c r="F16" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G16" t="n">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="H16" t="n">
         <v>7.9</v>
@@ -1898,7 +1898,7 @@
         <v>4.61</v>
       </c>
       <c r="O16" t="n">
-        <v>186918834590</v>
+        <v>188464896455</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30000</v>
+        <v>311500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.61%</t>
+          <t>'-4.74%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="H17" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>31450</v>
+        <v>327000</v>
       </c>
       <c r="K17" t="n">
-        <v>31500</v>
+        <v>324000</v>
       </c>
       <c r="L17" t="n">
-        <v>31550</v>
+        <v>340500</v>
       </c>
       <c r="M17" t="n">
-        <v>29950</v>
+        <v>308500</v>
       </c>
       <c r="N17" t="n">
-        <v>11.44</v>
+        <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>71768482750</v>
+        <v>77286402000</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>635000</v>
       </c>
       <c r="Q17" t="n">
-        <v>15000</v>
+        <v>52600</v>
       </c>
       <c r="R17" t="n">
-        <v>-420000</v>
+        <v>-52000</v>
       </c>
       <c r="S17" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대한전선 주가 하락에 대한 실망감 표현. 추석 연휴 전 추가 하락 예측.</t>
+          <t>52주 신고가 돌파 시점 도래 및 40만원 이상 상승 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대한전선', '하락', '추세']</t>
+          <t>['가온전선', '신고가', '40만원']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>311000</v>
+        <v>29950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.89%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.66</v>
+        <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="H18" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>327000</v>
+        <v>31450</v>
       </c>
       <c r="K18" t="n">
-        <v>324000</v>
+        <v>31500</v>
       </c>
       <c r="L18" t="n">
-        <v>340500</v>
+        <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>308500</v>
+        <v>29950</v>
       </c>
       <c r="N18" t="n">
-        <v>1.96</v>
+        <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>76816086000</v>
+        <v>72927457225</v>
       </c>
       <c r="P18" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R18" t="n">
-        <v>-52000</v>
+        <v>-420000</v>
       </c>
       <c r="S18" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 40만원 이상 상승 전망. 외인 매수세 유입.</t>
+          <t>대한전선 주가 하락에 대한 실망감 표현. 추석 연휴 전 추가 하락 예측.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['신고가', '외국인', '고평가']</t>
+          <t>['대한전선', '하락', '추세']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27950</v>
+        <v>28400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-25.27%</t>
+          <t>'-24.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="F19" t="n">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="G19" t="n">
-        <v>1253</v>
+        <v>1273</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>89881053750</v>
+        <v>93361759975</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_12.xlsx
+++ b/data/trending_integrated_20260921_12.xlsx
@@ -578,13 +578,13 @@
         <v>-0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H2" t="n">
         <v>0.35</v>
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203601158285</v>
+        <v>203688624285</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10780</v>
+        <v>10810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.51%</t>
+          <t>'+19.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>223072164600</v>
+        <v>225188340580</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20550</v>
+        <v>20450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.26%</t>
+          <t>'+10.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>75487475370</v>
+        <v>76153742520</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>신규형냐들의 진입 및 21000원 안착 기대, 키트루다 능가 삼중항체 기술 개발.</t>
+          <t>연기금 입성 및 신규 호재 기대감, 키트루다 능가 삼중항체 개발로 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['인제니아테라퓨틱스', '삼중항체', '신규진입']</t>
+          <t>['연기금', '삼중항체', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5860</v>
+        <v>5930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+7.92%</t>
+          <t>'+9.21%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H5" t="n">
         <v>0.19</v>
@@ -886,7 +886,7 @@
         <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>59520532470</v>
+        <v>59851593680</v>
       </c>
       <c r="P5" t="n">
         <v>13140</v>
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31800</v>
+        <v>11370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.25%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>393</v>
+        <v>107</v>
       </c>
       <c r="F6" t="n">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>1716</v>
+        <v>286</v>
       </c>
       <c r="H6" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K6" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L6" t="n">
-        <v>33400</v>
+        <v>12190</v>
       </c>
       <c r="M6" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N6" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O6" t="n">
-        <v>26456547350</v>
+        <v>181462515715</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R6" t="n">
-        <v>-148000</v>
+        <v>-6000</v>
       </c>
       <c r="S6" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 과정에서 제품명 조건부 수용 관련 내용, 리보세라닙 동일시 우려. 투자자 손실 관련 경고.</t>
+          <t>미국 광통신주 급등에 따른 관심 증가, 그러나 목표가와 폭락 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA', '신약 승인', '리보세라닙']</t>
+          <t>['광통신주', '추세', '공시']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208000</v>
+        <v>31850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.07%</t>
+          <t>'+7.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.09</v>
+        <v>-0.48</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>402</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>233</v>
       </c>
       <c r="G7" t="n">
-        <v>320</v>
+        <v>1787</v>
       </c>
       <c r="H7" t="n">
-        <v>75.44</v>
+        <v>16.67</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>196100</v>
+        <v>29650</v>
       </c>
       <c r="K7" t="n">
-        <v>199800</v>
+        <v>30400</v>
       </c>
       <c r="L7" t="n">
-        <v>208000</v>
+        <v>33400</v>
       </c>
       <c r="M7" t="n">
-        <v>199600</v>
+        <v>29400</v>
       </c>
       <c r="N7" t="n">
-        <v>75.53</v>
+        <v>17.15</v>
       </c>
       <c r="O7" t="n">
-        <v>558186172550</v>
+        <v>27468108900</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>69200</v>
       </c>
       <c r="Q7" t="n">
-        <v>64700</v>
+        <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>504000</v>
+        <v>-148000</v>
       </c>
       <c r="S7" t="n">
-        <v>-25000</v>
+        <v>-7000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
+          <t>FDA 신약 승인 과정 관련 혼란, NDA 통과 가능성 및 임상 실패 우려 공존, 매도 권유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당', '자사주', '외인']</t>
+          <t>['FDA', '신약 승인', '임상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11110</v>
+        <v>208000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.61%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="H8" t="n">
-        <v>18.29</v>
+        <v>75.44</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10520</v>
+        <v>196100</v>
       </c>
       <c r="K8" t="n">
-        <v>10780</v>
+        <v>199800</v>
       </c>
       <c r="L8" t="n">
-        <v>12190</v>
+        <v>208000</v>
       </c>
       <c r="M8" t="n">
-        <v>10590</v>
+        <v>199600</v>
       </c>
       <c r="N8" t="n">
-        <v>18.13</v>
+        <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>173832762205</v>
+        <v>567170687800</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1760</v>
+        <v>64700</v>
       </c>
       <c r="R8" t="n">
-        <v>-6000</v>
+        <v>504000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-25000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 시장 광통신주 급등에 따른 재진입 및 20% 상승 기대.</t>
+          <t>삼성전자우, 배당 기대감 속 주가 상승 전망. 자사주 취득 및 소각, 외인 매수세 유입 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신주', '재진입', '폭등']</t>
+          <t>['배당', '자사주', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="G9" t="n">
-        <v>2840</v>
+        <v>2920</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3588253415250</v>
+        <v>3703062132250</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>추석 전 30만원 돌파 기대 및 3분기 실적 발표 및 배당금 지급 예정.</t>
+          <t>신한증권 시스템 오류 속 외인 대규모 매수, HBM 경쟁 우위 및 목표가 30만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['삼성전자', '배당금', '실적발표']</t>
+          <t>['외인', 'HBM', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1873000</v>
+        <v>1872000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+0.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>483</v>
       </c>
       <c r="G10" t="n">
-        <v>2276</v>
+        <v>2246</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2859853846000</v>
+        <v>2940295043500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 반도체주 급등에 따른 SK하이닉스 20만원 돌파 및 상승세 전망.</t>
+          <t>신한증권 시스템 오류 발생, 미증시 반도체주 급등에 따른 200 향한 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '반도체', '상승세']</t>
+          <t>['반도체', '상승', '신한증권']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13690</v>
+        <v>26500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.30%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F11" t="n">
         <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>324</v>
+        <v>143</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13870</v>
+        <v>26800</v>
       </c>
       <c r="K11" t="n">
-        <v>14070</v>
+        <v>27400</v>
       </c>
       <c r="L11" t="n">
-        <v>14790</v>
+        <v>27750</v>
       </c>
       <c r="M11" t="n">
-        <v>13610</v>
+        <v>25650</v>
       </c>
       <c r="N11" t="n">
-        <v>4.92</v>
+        <v>2.41</v>
       </c>
       <c r="O11" t="n">
-        <v>62345385720</v>
+        <v>111673811200</v>
       </c>
       <c r="P11" t="n">
-        <v>30200</v>
+        <v>59600</v>
       </c>
       <c r="Q11" t="n">
-        <v>3540</v>
+        <v>1030</v>
       </c>
       <c r="R11" t="n">
-        <v>-298000</v>
+        <v>-234000</v>
       </c>
       <c r="S11" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26450</v>
+        <v>13670</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-1.44%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.3</v>
+        <v>0.58</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>327</v>
       </c>
       <c r="H12" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>26800</v>
+        <v>13870</v>
       </c>
       <c r="K12" t="n">
-        <v>27400</v>
+        <v>14070</v>
       </c>
       <c r="L12" t="n">
-        <v>27750</v>
+        <v>14790</v>
       </c>
       <c r="M12" t="n">
-        <v>25650</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
-        <v>2.41</v>
+        <v>4.92</v>
       </c>
       <c r="O12" t="n">
-        <v>110469973225</v>
+        <v>62894521010</v>
       </c>
       <c r="P12" t="n">
-        <v>59600</v>
+        <v>30200</v>
       </c>
       <c r="Q12" t="n">
-        <v>1030</v>
+        <v>3540</v>
       </c>
       <c r="R12" t="n">
-        <v>-234000</v>
+        <v>-298000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18470</v>
+        <v>18460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.38%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>65419531020</v>
+        <v>66143031290</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1682,13 +1682,13 @@
         <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="H14" t="n">
         <v>10.58</v>
@@ -1714,7 +1714,7 @@
         <v>10.68</v>
       </c>
       <c r="O14" t="n">
-        <v>93833864900</v>
+        <v>94766381750</v>
       </c>
       <c r="P14" t="n">
         <v>184000</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4115</v>
+        <v>4080</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.49%</t>
+          <t>'-3.32%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.22</v>
       </c>
       <c r="E15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="H15" t="n">
         <v>0.33</v>
@@ -1800,13 +1800,13 @@
         <v>4415</v>
       </c>
       <c r="M15" t="n">
-        <v>4105</v>
+        <v>4070</v>
       </c>
       <c r="N15" t="n">
         <v>0.55</v>
       </c>
       <c r="O15" t="n">
-        <v>27983982834</v>
+        <v>28753713720</v>
       </c>
       <c r="P15" t="n">
         <v>6480</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미투온, 미버스 관련 코인주 동반 상승 속 거래량 부진 및 재료 소멸 우려. 매도 물량 출회 가능성.</t>
+          <t>재료 불확실성 속 물량 넘기기 및 재료 소멸 가능성 언급, 5일선 이탈 하락 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['미버스', '거래량', '재료소멸']</t>
+          <t>['재료', '물량', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17630</v>
+        <v>17670</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.77%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3.29</v>
       </c>
       <c r="E16" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F16" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G16" t="n">
-        <v>908</v>
+        <v>941</v>
       </c>
       <c r="H16" t="n">
         <v>7.9</v>
@@ -1898,7 +1898,7 @@
         <v>4.61</v>
       </c>
       <c r="O16" t="n">
-        <v>188464896455</v>
+        <v>190467855820</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 대한광통신 주가 상승 기대감. 연말/내년 초까지 상승 전망.</t>
+          <t>미국 광통신주 급등, 기관 매수세 유입으로 3만원 돌파 및 연말까지 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대한광통신', '광통신주', '전망']</t>
+          <t>['광통신', '기관', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>311500</v>
+        <v>312250</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.74%</t>
+          <t>'-4.51%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H17" t="n">
         <v>3.62</v>
@@ -1990,7 +1990,7 @@
         <v>1.96</v>
       </c>
       <c r="O17" t="n">
-        <v>77286402000</v>
+        <v>77994030000</v>
       </c>
       <c r="P17" t="n">
         <v>635000</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29950</v>
+        <v>29900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.48</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F18" t="n">
         <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="H18" t="n">
         <v>11.92</v>
@@ -2076,13 +2076,13 @@
         <v>31550</v>
       </c>
       <c r="M18" t="n">
-        <v>29950</v>
+        <v>29900</v>
       </c>
       <c r="N18" t="n">
         <v>11.44</v>
       </c>
       <c r="O18" t="n">
-        <v>72927457225</v>
+        <v>75856445050</v>
       </c>
       <c r="P18" t="n">
         <v>75900</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>대한전선 주가 하락에 대한 실망감 표현. 추석 연휴 전 추가 하락 예측.</t>
+          <t>금요일 매도 후 재상승 기대했으나 하락, 추석 연휴 전 추가 하락 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['대한전선', '하락', '추세']</t>
+          <t>['매수', '하락', '추매']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28400</v>
+        <v>28650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-24.06%</t>
+          <t>'-23.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="F19" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="G19" t="n">
-        <v>1273</v>
+        <v>1323</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>93361759975</v>
+        <v>101388261475</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>

--- a/data/trending_integrated_20260921_12.xlsx
+++ b/data/trending_integrated_20260921_12.xlsx
@@ -610,7 +610,7 @@
         <v>0.39</v>
       </c>
       <c r="O2" t="n">
-        <v>203688624285</v>
+        <v>203727080035</v>
       </c>
       <c r="P2" t="n">
         <v>39350</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10810</v>
+        <v>10895</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.84%</t>
+          <t>'+20.79%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.09</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H3" t="n">
         <v>8.6</v>
@@ -702,7 +702,7 @@
         <v>8.51</v>
       </c>
       <c r="O3" t="n">
-        <v>225188340580</v>
+        <v>228409876255</v>
       </c>
       <c r="P3" t="n">
         <v>11640</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SFA반도체, 후공정 대장주로서 급등세. 전고점 돌파 및 15,000원 목표가 제시. 공매도 숏커버 기대.</t>
+          <t>후공정 대장주로 부각되며 강한 거래대금 동반 상승. 내년 전망 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['후공정', '급등', '목표가']</t>
+          <t>['후공정', '대장주', '거래대금']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20450</v>
+        <v>20300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.72%</t>
+          <t>'+9.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.27</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H4" t="n">
         <v>1.25</v>
@@ -794,7 +794,7 @@
         <v>0.98</v>
       </c>
       <c r="O4" t="n">
-        <v>76153742520</v>
+        <v>77723982320</v>
       </c>
       <c r="P4" t="n">
         <v>21600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5930</v>
+        <v>5900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.21%</t>
+          <t>'+8.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H5" t="n">
         <v>0.19</v>
@@ -886,7 +886,7 @@
         <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>59851593680</v>
+        <v>60084393350</v>
       </c>
       <c r="P5" t="n">
         <v>13140</v>
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11370</v>
+        <v>32000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+7.93%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-0.48</v>
       </c>
       <c r="E6" t="n">
-        <v>107</v>
+        <v>407</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>235</v>
       </c>
       <c r="G6" t="n">
-        <v>286</v>
+        <v>1838</v>
       </c>
       <c r="H6" t="n">
-        <v>18.29</v>
+        <v>16.67</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10520</v>
+        <v>29650</v>
       </c>
       <c r="K6" t="n">
-        <v>10780</v>
+        <v>30400</v>
       </c>
       <c r="L6" t="n">
-        <v>12190</v>
+        <v>33400</v>
       </c>
       <c r="M6" t="n">
-        <v>10590</v>
+        <v>29400</v>
       </c>
       <c r="N6" t="n">
-        <v>18.13</v>
+        <v>17.15</v>
       </c>
       <c r="O6" t="n">
-        <v>181462515715</v>
+        <v>28385925200</v>
       </c>
       <c r="P6" t="n">
-        <v>22450</v>
+        <v>69200</v>
       </c>
       <c r="Q6" t="n">
-        <v>1760</v>
+        <v>24150</v>
       </c>
       <c r="R6" t="n">
-        <v>-6000</v>
+        <v>-148000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등에 따른 관심 증가, 그러나 목표가와 폭락 가능성 언급.</t>
+          <t>미국 FDA 신약 승인 관련 기대와 불확실성 혼재. 과거 패턴 반복 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광통신주', '추세', '공시']</t>
+          <t>['FDA', '신약승인', '담관암']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31850</v>
+        <v>11240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.42%</t>
+          <t>'+6.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>402</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>233</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>1787</v>
+        <v>350</v>
       </c>
       <c r="H7" t="n">
-        <v>16.67</v>
+        <v>18.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>29650</v>
+        <v>10520</v>
       </c>
       <c r="K7" t="n">
-        <v>30400</v>
+        <v>10780</v>
       </c>
       <c r="L7" t="n">
-        <v>33400</v>
+        <v>12190</v>
       </c>
       <c r="M7" t="n">
-        <v>29400</v>
+        <v>10590</v>
       </c>
       <c r="N7" t="n">
-        <v>17.15</v>
+        <v>18.13</v>
       </c>
       <c r="O7" t="n">
-        <v>27468108900</v>
+        <v>188063998555</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>1760</v>
       </c>
       <c r="R7" t="n">
-        <v>-148000</v>
+        <v>-6000</v>
       </c>
       <c r="S7" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>FDA 신약 승인 과정 관련 혼란, NDA 통과 가능성 및 임상 실패 우려 공존, 매도 권유.</t>
+          <t>미국 광통신주 급등에 따른 영향 기대. 공시 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA', '신약 승인', '임상']</t>
+          <t>['광통신', '공시', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H8" t="n">
         <v>75.44</v>
@@ -1162,7 +1162,7 @@
         <v>75.53</v>
       </c>
       <c r="O8" t="n">
-        <v>567170687800</v>
+        <v>578744922300</v>
       </c>
       <c r="P8" t="n">
         <v>243500</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>273500</v>
+        <v>274000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+4.98%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="G9" t="n">
-        <v>2920</v>
+        <v>2863</v>
       </c>
       <c r="H9" t="n">
         <v>46.46</v>
@@ -1254,7 +1254,7 @@
         <v>46.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3703062132250</v>
+        <v>3788865276500</v>
       </c>
       <c r="P9" t="n">
         <v>374500</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신한증권 시스템 오류 속 외인 대규모 매수, HBM 경쟁 우위 및 목표가 30만원 돌파 기대.</t>
+          <t>외인 매수세 유입 및 3분기 잠정실적 발표 기대. BNK증권 목표가 27만원 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인', 'HBM', '목표가']</t>
+          <t>['외인매수', '실적발표', '목표주가']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1872000</v>
+        <v>1874500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.81%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G10" t="n">
-        <v>2246</v>
+        <v>2278</v>
       </c>
       <c r="H10" t="n">
         <v>50.23</v>
@@ -1346,7 +1346,7 @@
         <v>50.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2940295043500</v>
+        <v>3015226447500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26500</v>
+        <v>13690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.3</v>
+        <v>0.58</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>143</v>
+        <v>324</v>
       </c>
       <c r="H11" t="n">
-        <v>2.11</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>26800</v>
+        <v>13870</v>
       </c>
       <c r="K11" t="n">
-        <v>27400</v>
+        <v>14070</v>
       </c>
       <c r="L11" t="n">
-        <v>27750</v>
+        <v>14790</v>
       </c>
       <c r="M11" t="n">
-        <v>25650</v>
+        <v>13610</v>
       </c>
       <c r="N11" t="n">
-        <v>2.41</v>
+        <v>4.92</v>
       </c>
       <c r="O11" t="n">
-        <v>111673811200</v>
+        <v>63330686475</v>
       </c>
       <c r="P11" t="n">
-        <v>59600</v>
+        <v>30200</v>
       </c>
       <c r="Q11" t="n">
-        <v>1030</v>
+        <v>3540</v>
       </c>
       <c r="R11" t="n">
-        <v>-234000</v>
+        <v>-298000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
+          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI', '광통신', '목표가']</t>
+          <t>['원전', '신한투자증권', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13670</v>
+        <v>26300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.44%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.58</v>
+        <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>327</v>
+        <v>145</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13870</v>
+        <v>26800</v>
       </c>
       <c r="K12" t="n">
-        <v>14070</v>
+        <v>27400</v>
       </c>
       <c r="L12" t="n">
-        <v>14790</v>
+        <v>27750</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>25650</v>
       </c>
       <c r="N12" t="n">
-        <v>4.92</v>
+        <v>2.41</v>
       </c>
       <c r="O12" t="n">
-        <v>62894521010</v>
+        <v>113009840475</v>
       </c>
       <c r="P12" t="n">
-        <v>30200</v>
+        <v>59600</v>
       </c>
       <c r="Q12" t="n">
-        <v>3540</v>
+        <v>1030</v>
       </c>
       <c r="R12" t="n">
-        <v>-298000</v>
+        <v>-234000</v>
       </c>
       <c r="S12" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>원전 관련 기대감 언급. 신한투자증권의 공매도 의혹 및 주가 하락에 대한 불만.</t>
+          <t>성호전자, 미국 광통신 AI주 동반 상승 및 외인/기관 매수세 유입. 3만원 목표가 제시 및 투경 관련 논의.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '신한투자증권', '공매도']</t>
+          <t>['AI', '광통신', '목표가']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18460</v>
+        <v>18440</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="H13" t="n">
         <v>10.74</v>
@@ -1622,7 +1622,7 @@
         <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>66143031290</v>
+        <v>66997547735</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>공매도 장부 조작 의혹 제기 및 대차해지 운동 동참 요구.</t>
+          <t>공매도 장부 조작 의혹 제기 및 대차해지 운동 독려. 추세 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대우건설', '공매도', '대차해지']</t>
+          <t>['공매도', '대차해지', '추세']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78100</v>
+        <v>77900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.38%</t>
+          <t>'-2.62%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F14" t="n">
         <v>83</v>
       </c>
       <c r="G14" t="n">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="H14" t="n">
         <v>10.58</v>
@@ -1714,7 +1714,7 @@
         <v>10.68</v>
       </c>
       <c r="O14" t="n">
-        <v>94766381750</v>
+        <v>95637493200</v>
       </c>
       <c r="P14" t="n">
         <v>184000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>K-방산 시장 성장 및 한화시스템의 유럽 드론 시장 진출 기대, 공매도 금지 요구.</t>
+          <t>유럽 드론 시장 확대에 따른 K-방산 수혜 기대. 공매도 청산 및 10만원 돌파 가능성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['한화시스템', 'K-방산', '드론']</t>
+          <t>['드론', 'K-방산', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4080</v>
+        <v>17645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.32%</t>
+          <t>'-3.68%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.22</v>
+        <v>3.29</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>203</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="G15" t="n">
-        <v>284</v>
+        <v>961</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4220</v>
+        <v>18320</v>
       </c>
       <c r="K15" t="n">
-        <v>4220</v>
+        <v>18450</v>
       </c>
       <c r="L15" t="n">
-        <v>4415</v>
+        <v>18590</v>
       </c>
       <c r="M15" t="n">
-        <v>4070</v>
+        <v>17590</v>
       </c>
       <c r="N15" t="n">
-        <v>0.55</v>
+        <v>4.61</v>
       </c>
       <c r="O15" t="n">
-        <v>28753713720</v>
+        <v>191861905005</v>
       </c>
       <c r="P15" t="n">
-        <v>6480</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>208000</v>
+        <v>-1480000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>재료 불확실성 속 물량 넘기기 및 재료 소멸 가능성 언급, 5일선 이탈 하락 우려.</t>
+          <t>미국 광통신주 급등에 따른 수혜 기대. 3만원 터치 가능성 및 연말까지 상승 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['재료', '물량', '하락']</t>
+          <t>['광통신', 'AI', '수출']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17670</v>
+        <v>4060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-3.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.29</v>
+        <v>-0.22</v>
       </c>
       <c r="E16" t="n">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>941</v>
+        <v>298</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>0.33</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18320</v>
+        <v>4220</v>
       </c>
       <c r="K16" t="n">
-        <v>18450</v>
+        <v>4220</v>
       </c>
       <c r="L16" t="n">
-        <v>18590</v>
+        <v>4415</v>
       </c>
       <c r="M16" t="n">
-        <v>17590</v>
+        <v>4045</v>
       </c>
       <c r="N16" t="n">
-        <v>4.61</v>
+        <v>0.55</v>
       </c>
       <c r="O16" t="n">
-        <v>190467855820</v>
+        <v>29199808127</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>6480</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>1738</v>
       </c>
       <c r="R16" t="n">
-        <v>-1480000</v>
+        <v>208000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신주 급등, 기관 매수세 유입으로 3만원 돌파 및 연말까지 상승 전망.</t>
+          <t>재료 소멸 및 5일선 하향 돌파로 인한 하락 가능성 언급. 물타기 및 신규 매수 금지.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '기관', '상승']</t>
+          <t>['재료소멸', '5일선', '개잡주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>312250</v>
+        <v>29950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.51%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.66</v>
+        <v>0.48</v>
       </c>
       <c r="E17" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="H17" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>327000</v>
+        <v>31450</v>
       </c>
       <c r="K17" t="n">
-        <v>324000</v>
+        <v>31500</v>
       </c>
       <c r="L17" t="n">
-        <v>340500</v>
+        <v>31550</v>
       </c>
       <c r="M17" t="n">
-        <v>308500</v>
+        <v>29900</v>
       </c>
       <c r="N17" t="n">
-        <v>1.96</v>
+        <v>11.44</v>
       </c>
       <c r="O17" t="n">
-        <v>77994030000</v>
+        <v>76970717475</v>
       </c>
       <c r="P17" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
-        <v>-52000</v>
+        <v>-420000</v>
       </c>
       <c r="S17" t="n">
-        <v>-2000</v>
+        <v>-8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 시점 도래 및 40만원 이상 상승 기대.</t>
+          <t>연이은 하락세에 대한 불만 표출. 다음 날 추가 하락 예측.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['가온전선', '신고가', '40만원']</t>
+          <t>['하락', '추매', '대장']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29900</v>
+        <v>310500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-5.05%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="E18" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="H18" t="n">
-        <v>11.92</v>
+        <v>3.62</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31450</v>
+        <v>327000</v>
       </c>
       <c r="K18" t="n">
-        <v>31500</v>
+        <v>324000</v>
       </c>
       <c r="L18" t="n">
-        <v>31550</v>
+        <v>340500</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>308500</v>
       </c>
       <c r="N18" t="n">
-        <v>11.44</v>
+        <v>1.96</v>
       </c>
       <c r="O18" t="n">
-        <v>75856445050</v>
+        <v>78829432750</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>635000</v>
       </c>
       <c r="Q18" t="n">
-        <v>15000</v>
+        <v>52600</v>
       </c>
       <c r="R18" t="n">
-        <v>-420000</v>
+        <v>-52000</v>
       </c>
       <c r="S18" t="n">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>금요일 매도 후 재상승 기대했으나 하락, 추석 연휴 전 추가 하락 전망.</t>
+          <t>52주 신고가 돌파 시도. 40만원 돌파 및 고평가 논란.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['매수', '하락', '추매']</t>
+          <t>['신고가', '고평가', '돌파']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28650</v>
+        <v>28350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-23.40%</t>
+          <t>'-24.20%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="F19" t="n">
         <v>362</v>
       </c>
       <c r="G19" t="n">
-        <v>1323</v>
+        <v>1348</v>
       </c>
       <c r="H19" t="n">
         <v>7.09</v>
@@ -2174,7 +2174,7 @@
         <v>7.08</v>
       </c>
       <c r="O19" t="n">
-        <v>101388261475</v>
+        <v>104602916750</v>
       </c>
       <c r="P19" t="n">
         <v>146600</v>
